--- a/tests/fixtures/formula-import.xlsx
+++ b/tests/fixtures/formula-import.xlsx
@@ -2,9 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R09d515f0c8f340b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R9bfc6d7550ed4a7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="3" r:id="R96baf1c322504db0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="Re224613c51564007"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R91f89916cd924161"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R4b0c6284a98d46cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="Re106b35b58bb4c64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R130678dc730e4b0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="6" r:id="R5f6154b1c360498a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,6 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
@@ -60,7 +66,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -88,6 +94,7 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -395,13 +402,14 @@
   <x:cols>
     <x:col min="1" max="1" width="9.779999732971191" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.889999866485596" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="13.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="5.889999866485596" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.109999656677246" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -412,24 +420,27 @@
         <x:v>specialty_code</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
+        <x:v>curriculum_code</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
         <x:v>course</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>education_form</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>headcount</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>program_base</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>study_week_type</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="I1" s="6" t="str">
         <x:v>primary_building_code</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="J1" s="6" t="str">
         <x:v>subgroup_count</x:v>
       </x:c>
     </x:row>
@@ -440,25 +451,28 @@
       <x:c r="B2" s="7" t="str">
         <x:v>09.02.07</x:v>
       </x:c>
-      <x:c r="C2" s="7" t="n">
+      <x:c r="C2" s="7" t="str">
+        <x:v>UP-09.02.07-2026</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D2" s="7" t="str">
+      <x:c r="E2" s="7" t="str">
         <x:v>full_time</x:v>
       </x:c>
-      <x:c r="E2" s="7" t="n">
+      <x:c r="F2" s="7" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F2" s="7" t="str">
+      <x:c r="G2" s="7" t="str">
         <x:v>9_classes</x:v>
       </x:c>
-      <x:c r="G2" s="7" t="str">
+      <x:c r="H2" s="7" t="str">
         <x:v>six_days</x:v>
       </x:c>
-      <x:c r="H2" s="7" t="str">
+      <x:c r="I2" s="7" t="str">
         <x:v>MAIN</x:v>
       </x:c>
-      <x:c r="I2" s="7" t="n">
+      <x:c r="J2" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -468,6 +482,196 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38.11000061035156" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34.11000061035156" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="5.110000133514404" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>specialty_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>specialty_name</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>qualification</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>program_base</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>education_form</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>09.02.07</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>Информационные системы и программирование</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>Специалист по информационным системам</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>full_time</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="6.559999942779541" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="5.329999923706055" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>curriculum_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>specialty_code</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>admission_year</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>valid_from</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>valid_to</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>UP-09.02.07-2026</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>09.02.07</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="7" t="str">
+        <x:v>active</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="21.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.78000020980835" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10.4399995803833" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>curriculum_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>discipline_code</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>discipline_name</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>section_code</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>semester</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>lesson_type</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>planned_hours</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>control_form</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>UP-09.02.07-2026</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>MDK.01.01</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>Основы программирования</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>ПМ.01</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>practice</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>credit</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>

--- a/tests/fixtures/formula-import.xlsx
+++ b/tests/fixtures/formula-import.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="Re224613c51564007"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R91f89916cd924161"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R4b0c6284a98d46cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="Re106b35b58bb4c64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R130678dc730e4b0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="6" r:id="R5f6154b1c360498a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R0b66a748ce064cc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="Ra4f0d0bf916245eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="Rda476ef935e54673"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="Rba1499eab17b4a86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R95051c2283c94fe8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="Rb38eaf2c31e54a31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="7" r:id="R8c0685a6fbaf441e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -675,6 +676,75 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="11.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="5.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>student_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>full_name</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>group_code</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>enrollment_date</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>end_date</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>subgroup_codes</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>elective_codes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>S-001</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>Петров Пётр Петрович</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>ИС-101</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>active</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="7" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>WEB</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="16.110000610351562" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12.220000267028809" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="7.78000020980835" hidden="0" customWidth="1"/>

--- a/tests/fixtures/formula-import.xlsx
+++ b/tests/fixtures/formula-import.xlsx
@@ -2,13 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R0b66a748ce064cc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="Ra4f0d0bf916245eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="Rda476ef935e54673"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="Rba1499eab17b4a86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R95051c2283c94fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="Rb38eaf2c31e54a31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="7" r:id="R8c0685a6fbaf441e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R6bd663c9ee7f46dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R5144b9753eef4871"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R0033eb10e51444f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="Raa6879a5fa6047ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="Rae5d6d3d1ce345ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R0e5f4c5af9ed4faf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R145fb25f3ee6429a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="Rbc87389d1d844a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="R68881d1edce44e12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="R429f29000edb401b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="R2d4448ca7fc54ef6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -397,6 +401,198 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="5.110000133514404" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>room_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>room_name</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>building_code</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>room_type_code</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>capacity</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>equipment_codes</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>MAIN-201</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>Лаборатория 201</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>MAIN</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>COMPUTER_LAB</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>COMPUTERS</x:v>
+      </x:c>
+      <x:c r="G2" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.78000020980835" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.889999866485596" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="5.889999866485596" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="11.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="9.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="17.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="9" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="21.559999465942383" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>workload_row_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>academic_year</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>semester</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>discipline_code</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>discipline_name</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>group_code</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>subgroup</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>stream</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>teacher_code</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
+        <x:v>lesson_type</x:v>
+      </x:c>
+      <x:c r="K1" s="6" t="str">
+        <x:v>total_academic_hours</x:v>
+      </x:c>
+      <x:c r="L1" s="6" t="str">
+        <x:v>event_duration_hours</x:v>
+      </x:c>
+      <x:c r="M1" s="6" t="str">
+        <x:v>recurrence</x:v>
+      </x:c>
+      <x:c r="N1" s="6" t="str">
+        <x:v>lesson_bundle_code</x:v>
+      </x:c>
+      <x:c r="O1" s="6" t="str">
+        <x:v>room_type</x:v>
+      </x:c>
+      <x:c r="P1" s="6" t="str">
+        <x:v>room_capacity</x:v>
+      </x:c>
+      <x:c r="Q1" s="6" t="str">
+        <x:v>required_equipment_codes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>W-001</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>MDK.01.01</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>Основы программирования</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>ИС-101</x:v>
+      </x:c>
+      <x:c r="G2" s="7"/>
+      <x:c r="H2" s="7"/>
+      <x:c r="I2" s="7" t="str">
+        <x:v>T-001</x:v>
+      </x:c>
+      <x:c r="J2" s="7" t="str">
+        <x:v>practice</x:v>
+      </x:c>
+      <x:c r="K2" s="7" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L2" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M2" s="7" t="str">
+        <x:v>weekly</x:v>
+      </x:c>
+      <x:c r="N2" s="7"/>
+      <x:c r="O2" s="7" t="str">
+        <x:v>computer_lab</x:v>
+      </x:c>
+      <x:c r="P2" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Q2" s="7" t="str">
+        <x:v>COMPUTERS</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -745,116 +941,103 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.220000267028809" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="7.78000020980835" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="21.780000686645508" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="7.889999866485596" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="5.889999866485596" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="17.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="17.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="9" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="10.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>workload_row_code</x:v>
+        <x:v>building_code</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>academic_year</x:v>
+        <x:v>building_name</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>semester</x:v>
-      </x:c>
-      <x:c r="D1" s="6" t="str">
-        <x:v>discipline_code</x:v>
-      </x:c>
-      <x:c r="E1" s="6" t="str">
-        <x:v>discipline_name</x:v>
-      </x:c>
-      <x:c r="F1" s="6" t="str">
-        <x:v>group_code</x:v>
-      </x:c>
-      <x:c r="G1" s="6" t="str">
-        <x:v>subgroup</x:v>
-      </x:c>
-      <x:c r="H1" s="6" t="str">
-        <x:v>stream</x:v>
-      </x:c>
-      <x:c r="I1" s="6" t="str">
-        <x:v>teacher_code</x:v>
-      </x:c>
-      <x:c r="J1" s="6" t="str">
-        <x:v>lesson_type</x:v>
-      </x:c>
-      <x:c r="K1" s="6" t="str">
-        <x:v>total_academic_hours</x:v>
-      </x:c>
-      <x:c r="L1" s="6" t="str">
-        <x:v>event_duration_hours</x:v>
-      </x:c>
-      <x:c r="M1" s="6" t="str">
-        <x:v>recurrence</x:v>
-      </x:c>
-      <x:c r="N1" s="6" t="str">
-        <x:v>lesson_bundle_code</x:v>
-      </x:c>
-      <x:c r="O1" s="6" t="str">
-        <x:v>room_type</x:v>
-      </x:c>
-      <x:c r="P1" s="6" t="str">
-        <x:v>room_capacity</x:v>
+        <x:v>active</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>W-001</x:v>
+        <x:v>MAIN</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026/2027</x:v>
-      </x:c>
-      <x:c r="C2" s="7" t="n">
+        <x:v>Главный корпус</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D2" s="7" t="str">
-        <x:v>MDK.01.01</x:v>
-      </x:c>
-      <x:c r="E2" s="7" t="str">
-        <x:v>Основы программирования</x:v>
-      </x:c>
-      <x:c r="F2" s="7" t="str">
-        <x:v>ИС-101</x:v>
-      </x:c>
-      <x:c r="G2" s="7"/>
-      <x:c r="H2" s="7"/>
-      <x:c r="I2" s="7" t="str">
-        <x:v>T-001</x:v>
-      </x:c>
-      <x:c r="J2" s="7" t="str">
-        <x:v>practice</x:v>
-      </x:c>
-      <x:c r="K2" s="7" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="L2" s="7" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M2" s="7" t="str">
-        <x:v>weekly</x:v>
-      </x:c>
-      <x:c r="N2" s="7"/>
-      <x:c r="O2" s="7" t="str">
-        <x:v>computer_lab</x:v>
-      </x:c>
-      <x:c r="P2" s="7" t="n">
-        <x:v>25</x:v>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>room_type_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>room_type_name</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>COMPUTER_LAB</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>Компьютерный класс</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>equipment_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>equipment_name</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>COMPUTERS</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>Компьютеры</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="b">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/tests/fixtures/formula-import.xlsx
+++ b/tests/fixtures/formula-import.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R6bd663c9ee7f46dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R5144b9753eef4871"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R0033eb10e51444f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="Raa6879a5fa6047ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="Rae5d6d3d1ce345ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R0e5f4c5af9ed4faf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R145fb25f3ee6429a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="Rbc87389d1d844a5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="R68881d1edce44e12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="R429f29000edb401b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="R2d4448ca7fc54ef6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="Raff555a437f64c44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="Rd49f67556cad49ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="Rfbc810744b964504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R893de2413b854c1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="Red4215b796284609"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R5e35b220f2094a86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R5d13bc032849452a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="Re24e0adf775c466a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="R90b4754672e04171"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="R8bcaee393170459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="Re70ae7204a114b79"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -319,48 +319,48 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.440000534057617" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="20.110000610351562" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="23.559999465942383" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18.219999313354492" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.559999465942383" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16.559999465942383" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="5.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="7.21999979019165" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>teacher_code</x:v>
+        <x:v>Код преподавателя</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>full_name</x:v>
+        <x:v>ФИО</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>department</x:v>
+        <x:v>Подразделение</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>employment_type</x:v>
+        <x:v>Тип занятости</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>yearly_assigned_hours</x:v>
+        <x:v>Назначено часов в год</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>yearly_limit_hours</x:v>
+        <x:v>Лимит часов в год</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>max_hours_per_day</x:v>
+        <x:v>Макс. часов в день</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>max_days_per_week</x:v>
+        <x:v>Макс. дней в неделю</x:v>
       </x:c>
       <x:c r="I1" s="6" t="str">
-        <x:v>home_building_code</x:v>
+        <x:v>Основной корпус</x:v>
       </x:c>
       <x:c r="J1" s="6" t="str">
-        <x:v>active</x:v>
+        <x:v>Активен</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -405,36 +405,36 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.220000267028809" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="13.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="7.110000133514404" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="5.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.21999979019165" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>room_code</x:v>
+        <x:v>Код аудитории</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>room_name</x:v>
+        <x:v>Название аудитории</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>building_code</x:v>
+        <x:v>Код корпуса</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>room_type_code</x:v>
+        <x:v>Код типа помещения</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>capacity</x:v>
+        <x:v>Вместимость</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>equipment_codes</x:v>
+        <x:v>Коды оборудования</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>active</x:v>
+        <x:v>Активна</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -469,76 +469,76 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.220000267028809" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="7.78000020980835" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.559999942779541" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14.220000267028809" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="21.780000686645508" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="7.889999866485596" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="5.889999866485596" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="17.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="17.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="9" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="10.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="21.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="5.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="23.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="24.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="13.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="13.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="20.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="21.329999923706055" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>workload_row_code</x:v>
+        <x:v>Код строки нагрузки</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>academic_year</x:v>
+        <x:v>Учебный год</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>semester</x:v>
+        <x:v>Семестр</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>discipline_code</x:v>
+        <x:v>Код дисциплины</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>discipline_name</x:v>
+        <x:v>Название дисциплины</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>group_code</x:v>
+        <x:v>Код группы</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>subgroup</x:v>
+        <x:v>Подгруппа</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>stream</x:v>
+        <x:v>Поток</x:v>
       </x:c>
       <x:c r="I1" s="6" t="str">
-        <x:v>teacher_code</x:v>
+        <x:v>Код преподавателя</x:v>
       </x:c>
       <x:c r="J1" s="6" t="str">
-        <x:v>lesson_type</x:v>
+        <x:v>Вид занятия</x:v>
       </x:c>
       <x:c r="K1" s="6" t="str">
-        <x:v>total_academic_hours</x:v>
+        <x:v>Всего академических часов</x:v>
       </x:c>
       <x:c r="L1" s="6" t="str">
-        <x:v>event_duration_hours</x:v>
+        <x:v>Продолжительность занятия</x:v>
       </x:c>
       <x:c r="M1" s="6" t="str">
-        <x:v>recurrence</x:v>
+        <x:v>Периодичность</x:v>
       </x:c>
       <x:c r="N1" s="6" t="str">
-        <x:v>lesson_bundle_code</x:v>
+        <x:v>Код связки занятий</x:v>
       </x:c>
       <x:c r="O1" s="6" t="str">
-        <x:v>room_type</x:v>
+        <x:v>Тип помещения</x:v>
       </x:c>
       <x:c r="P1" s="6" t="str">
-        <x:v>room_capacity</x:v>
+        <x:v>Требуемая вместимость</x:v>
       </x:c>
       <x:c r="Q1" s="6" t="str">
-        <x:v>required_equipment_codes</x:v>
+        <x:v>Требуемое оборудование</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -597,48 +597,48 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="5.889999866485596" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="8.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="13.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="4.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.110000610351562" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>group_code</x:v>
+        <x:v>Код группы</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>specialty_code</x:v>
+        <x:v>Код специальности</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>curriculum_code</x:v>
+        <x:v>Код учебного плана</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>course</x:v>
+        <x:v>Курс</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>education_form</x:v>
+        <x:v>Форма обучения</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>headcount</x:v>
+        <x:v>Численность</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>program_base</x:v>
+        <x:v>База обучения</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>study_week_type</x:v>
+        <x:v>Тип учебной недели</x:v>
       </x:c>
       <x:c r="I1" s="6" t="str">
-        <x:v>primary_building_code</x:v>
+        <x:v>Основной корпус</x:v>
       </x:c>
       <x:c r="J1" s="6" t="str">
-        <x:v>subgroup_count</x:v>
+        <x:v>Количество подгрупп</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -682,32 +682,32 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.440000534057617" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="38.11000061035156" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34.11000061035156" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="5.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.21999979019165" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>specialty_code</x:v>
+        <x:v>Код специальности</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>specialty_name</x:v>
+        <x:v>Название специальности</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>qualification</x:v>
+        <x:v>Квалификация</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>program_base</x:v>
+        <x:v>База обучения</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>education_form</x:v>
+        <x:v>Форма обучения</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>active</x:v>
+        <x:v>Активна</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -739,36 +739,36 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="6.21999979019165" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="6.559999942779541" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="5.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.110000133514404" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>curriculum_code</x:v>
+        <x:v>Код учебного плана</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>specialty_code</x:v>
+        <x:v>Код специальности</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>admission_year</x:v>
+        <x:v>Год набора</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>version</x:v>
+        <x:v>Версия</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>valid_from</x:v>
+        <x:v>Действует с</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>valid_to</x:v>
+        <x:v>Действует по</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>status</x:v>
+        <x:v>Статус</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -801,40 +801,40 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.220000267028809" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="21.780000686645508" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="7.78000020980835" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="10.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.559999942779541" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.220000267028809" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>curriculum_code</x:v>
+        <x:v>Код учебного плана</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>discipline_code</x:v>
+        <x:v>Код дисциплины</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>discipline_name</x:v>
+        <x:v>Название дисциплины</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>section_code</x:v>
+        <x:v>Код раздела</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>semester</x:v>
+        <x:v>Семестр</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>lesson_type</x:v>
+        <x:v>Вид занятия</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>planned_hours</x:v>
+        <x:v>Плановые часы</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>control_form</x:v>
+        <x:v>Форма контроля</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -872,40 +872,40 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11.4399995803833" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="5.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="7.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.890000343322754" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>student_code</x:v>
+        <x:v>Код студента</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>full_name</x:v>
+        <x:v>ФИО</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>group_code</x:v>
+        <x:v>Код группы</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>status</x:v>
+        <x:v>Статус</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>enrollment_date</x:v>
+        <x:v>Дата зачисления</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>end_date</x:v>
+        <x:v>Дата окончания</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>subgroup_codes</x:v>
+        <x:v>Номера подгрупп</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>elective_codes</x:v>
+        <x:v>Коды элективов</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -941,20 +941,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.21999979019165" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>building_code</x:v>
+        <x:v>Код корпуса</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>building_name</x:v>
+        <x:v>Название корпуса</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>active</x:v>
+        <x:v>Активен</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -977,20 +977,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.21999979019165" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>room_type_code</x:v>
+        <x:v>Код типа помещения</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>room_type_name</x:v>
+        <x:v>Название типа помещения</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>active</x:v>
+        <x:v>Активен</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -1013,20 +1013,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.21999979019165" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>equipment_code</x:v>
+        <x:v>Код оборудования</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>equipment_name</x:v>
+        <x:v>Название оборудования</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>active</x:v>
+        <x:v>Активно</x:v>
       </x:c>
     </x:row>
     <x:row r="2">

--- a/tests/fixtures/formula-import.xlsx
+++ b/tests/fixtures/formula-import.xlsx
@@ -2,17 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="Raff555a437f64c44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="Rd49f67556cad49ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="Rfbc810744b964504"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R893de2413b854c1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="Red4215b796284609"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R5e35b220f2094a86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R5d13bc032849452a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="Re24e0adf775c466a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="R90b4754672e04171"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="R8bcaee393170459b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="Re70ae7204a114b79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="Re990ba98b8ad466a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="Rd914c15b35df40d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="Red8e53b7fac34cf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R7d3bd190be6d40dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="Rbce6c3d244a6450f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R2b5dcc94865d4a26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R469519ddbdc4409c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R35a601aa9345426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="R9b1cc6811ca746a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="R5fac137cac0042fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="Rfc66e181245143bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные годы" sheetId="12" r:id="Rca02ca4d59594c9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Периоды" sheetId="13" r:id="Rc4471b17980147c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сетка звонков" sheetId="14" r:id="Rd8846b9bb286499c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -593,6 +596,170 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.21999979019165" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Учебный год</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Дата начала</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Дата окончания</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Активен</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="n">
+        <x:v>46568</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.559999942779541" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Код периода</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Учебный год</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Название периода</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Тип периода</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Дата начала</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Дата окончания</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Семестр</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>SEM-1</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>Первый семестр</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>teaching</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="n">
+        <x:v>46384</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.4399995803833" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Код интервала</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Учебный год</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Код смены</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Номер занятия</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Начало</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Окончание</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>S1-01</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>S1</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>08:30</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>10:00</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>

--- a/tests/fixtures/formula-import.xlsx
+++ b/tests/fixtures/formula-import.xlsx
@@ -2,20 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="Re990ba98b8ad466a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="Rd914c15b35df40d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="Red8e53b7fac34cf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R7d3bd190be6d40dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="Rbce6c3d244a6450f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R2b5dcc94865d4a26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R469519ddbdc4409c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R35a601aa9345426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="R9b1cc6811ca746a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="R5fac137cac0042fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="Rfc66e181245143bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные годы" sheetId="12" r:id="Rca02ca4d59594c9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Периоды" sheetId="13" r:id="Rc4471b17980147c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сетка звонков" sheetId="14" r:id="Rd8846b9bb286499c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R6364164231f54b1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="Rc78341c64dec4a50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R06c3de5521c543a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R942ab6487ebf42e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R5cbb9b859a5240b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="Ra5a0bdeb17854d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R9b5dcb8ddd9e4dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R90f14cd59cbc40f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="Rac2062f696b04f7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="R601445eb8e31472b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="R4042dc217eb6478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные годы" sheetId="12" r:id="Rb1ae75a38b2e4027"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Периоды" sheetId="13" r:id="R9d63dd377f8b4df6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сетка звонков" sheetId="14" r:id="Ra39f26d6bbce4373"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Исключения календаря" sheetId="15" r:id="R63ad4b258f2d4723"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Недоступность" sheetId="16" r:id="R0d932fcb491b4ee9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -760,6 +762,140 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.440000534057617" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Код исключения</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Учебный год</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Тип исключения</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Дата исключения</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Перенос на дату</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Сокращённый день до</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Примечание</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>EX-001</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>holiday</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="n">
+        <x:v>46330</x:v>
+      </x:c>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="7"/>
+      <x:c r="G2" s="7" t="str">
+        <x:v>День народного единства</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.110000610351562" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Код недоступности</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Учебный год</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Тип ресурса</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Код ресурса</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Дата начала</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Дата окончания</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Время начала</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>Время окончания</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>Причина</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>U-001</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>teacher</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>T-001</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>46296</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G2" s="7"/>
+      <x:c r="H2" s="7"/>
+      <x:c r="I2" s="7" t="str">
+        <x:v>Повышение квалификации</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>

--- a/tests/fixtures/formula-import.xlsx
+++ b/tests/fixtures/formula-import.xlsx
@@ -2,22 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R6364164231f54b1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="Rc78341c64dec4a50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R06c3de5521c543a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R942ab6487ebf42e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R5cbb9b859a5240b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="Ra5a0bdeb17854d95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R9b5dcb8ddd9e4dd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R90f14cd59cbc40f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="Rac2062f696b04f7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="R601445eb8e31472b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="R4042dc217eb6478e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные годы" sheetId="12" r:id="Rb1ae75a38b2e4027"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Периоды" sheetId="13" r:id="R9d63dd377f8b4df6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сетка звонков" sheetId="14" r:id="Ra39f26d6bbce4373"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Исключения календаря" sheetId="15" r:id="R63ad4b258f2d4723"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Недоступность" sheetId="16" r:id="R0d932fcb491b4ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R1dd9334854fc4e3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="Rdbf701a024c34ef1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R04e293caff5f4698"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R3749ec94a9f2460f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R411d645f05d442ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="Rbd7256ee2e7642c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R830c6b568a61488f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R9a45b17bf88441bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="Rec1c9181288c45cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="Rfd17f49251b0401e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="R13a559467adf4700"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные годы" sheetId="12" r:id="R9d6316d0e84549ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные циклы" sheetId="13" r:id="Rad8cfccc6b2e4d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Периоды" sheetId="14" r:id="R2b0273a47301467d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сетка звонков" sheetId="15" r:id="R5f3eb102a767443c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Исключения календаря" sheetId="16" r:id="R70948f89131245bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Недоступность" sheetId="17" r:id="R36e74876b92046e8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -491,6 +492,8 @@
     <x:col min="15" max="15" width="13.109999656677246" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="20.440000534057617" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="21.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="23" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="18.219999313354492" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -544,6 +547,12 @@
       </x:c>
       <x:c r="Q1" s="6" t="str">
         <x:v>Требуемое оборудование</x:v>
+      </x:c>
+      <x:c r="R1" s="6" t="str">
+        <x:v>Код учебного цикла</x:v>
+      </x:c>
+      <x:c r="S1" s="6" t="str">
+        <x:v>Номера недель цикла</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -592,6 +601,12 @@
       <x:c r="Q2" s="7" t="str">
         <x:v>COMPUTERS</x:v>
       </x:c>
+      <x:c r="R2" s="7" t="str">
+        <x:v>NUMERATOR-DENOMINATOR</x:v>
+      </x:c>
+      <x:c r="S2" s="7" t="str">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -642,6 +657,63 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19.889999389648438" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.21999979019165" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Код цикла</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Учебный год</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Название цикла</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Длина цикла в неделях</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Дата начала отсчёта</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Активен</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>NUMERATOR-DENOMINATOR</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>Числитель / знаменатель</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -705,7 +777,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -762,7 +834,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -822,7 +894,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
